--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_06-02-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_06-02-2026.xlsx
@@ -2602,7 +2602,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
